--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Delivery Senior Consultant, Data Engineering and Conversion Solutions</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Google Cloud Platform, BigQuery, Spark, Scala, Snowflake, Talend, dbt</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6f3843c2e2f33e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior Machine Learning Engineer (MLOPS)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,112 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Software Engineer III - AI/ML Developer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Ellipsis Health</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>San Francisco, CA, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>11.8</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MDM Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>McLane Company</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Temple, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,145 +531,250 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Senior Machine Learning Engineer (MLOPS)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>The Coca-Cola Company</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Developer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ellipsis Health</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>MDM Integration Engineer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>McLane Company</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Temple, TX, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D10" t="n">
         <v>11.1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
         </is>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,40 +741,75 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Senior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ellipsis Health</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>MDM Integration Engineer</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>McLane Company</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Temple, TX, US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>11.1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
         </is>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -608,52 +608,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (MLOPS)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,24 +661,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdb054133d54c854</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Onsite_CCaaS - Five9 GCP Data Engineer_ Sunrise, FL || Charlotte, NC</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>SRM Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bonita Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, S3, SQS, SNS, RDS, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93687bce41c54bba</t>
+          <t>https://www.indeed.com/viewjob?jk=2ab3b7c309c34e68</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Onsite_CCaaS - Five9 GCP Data Engineer_ Sunrise, FL || Charlotte, NC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,24 +521,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=93687bce41c54bba</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,87 +731,192 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Software Engineer III - AI/ML Developer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ellipsis Health</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>MDM Integration Engineer</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>McLane Company</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Temple, TX, US USA</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>11.1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Test Frameworks &amp; Tooling</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20778a070554f061</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Onsite_CCaaS - Five9 GCP Data Engineer_ Sunrise, FL || Charlotte, NC</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93687bce41c54bba</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Onsite_CCaaS - Five9 GCP Data Engineer_ Sunrise, FL || Charlotte, NC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,24 +556,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=93687bce41c54bba</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,59 +696,59 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,122 +801,192 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3fcc35e91c6408</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>AI/ML Solutions Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II, Test Frameworks &amp; Tooling</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>10.4</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MySQL, CI/CD, Terraform, Kubernetes, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=20778a070554f061</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ARS/Rescue Rooter</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Onsite_CCaaS - Five9 GCP Data Engineer_ Sunrise, FL || Charlotte, NC</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, GCP, BigQuery, Cloud Storage, Hive, Spark, Scala, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93687bce41c54bba</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Engineer</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Vertex AI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Solutions Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,40 +951,215 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Senior DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ellipsis Health</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Microsoft Fabric Data Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Landmark Properties, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Athens, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ea4631bd176d0be</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Microsoft Fabric Data Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Landmark Properties, Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68a59ec1d4554527</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MDM Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>McLane Company</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Temple, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Azure Cloud Engineer</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>ARS/Rescue Rooter</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Memphis, TN, US USA</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D21" t="n">
         <v>10.4</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ea4631bd176d0be</t>
+          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68a59ec1d4554527</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Software Engineer, LLM Pipeline &amp; AI Agents</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>TSOLife</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, PostgreSQL, CI/CD, GitHub Actions, CodeBuild, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffa9745f98e8936</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Engineer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Vertex AI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI/ML Solutions Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr. Engineer - Software Development Engineering</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,40 +1126,285 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Senior Software Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MDM Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>McLane Company</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Temple, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>IIB and MQ Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, MySQL, Splunk, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7aa947e1b4b6a598</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Engineer â€“ Python/AI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ARS/Rescue Rooter</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>The Hershey Company</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hershey, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Software Engineer, LLM Pipeline &amp; AI Agents</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>TSOLife</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D28" t="n">
         <v>10.4</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>AWS, S3, IAM, PostgreSQL, CI/CD, GitHub Actions, CodeBuild, Docker, Kubernetes, pytest</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0ffa9745f98e8936</t>
         </is>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SRM Technologies</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bonita Springs, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, RDS, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Redshift, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, GCP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab3b7c309c34e68</t>
+          <t>https://www.indeed.com/viewjob?jk=335286c429f8d5b7</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure Infrastructure &amp; Databricks Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Photon, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ad6d99882cd158</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>SRM Technologies</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Bonita Springs, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, SQS, SNS, RDS, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
+          <t>https://www.indeed.com/viewjob?jk=2ab3b7c309c34e68</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hollstadt Consulting</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
+          <t>https://www.indeed.com/viewjob?jk=30fbcef65758a1bd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>API &amp; Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
+          <t>https://www.indeed.com/viewjob?jk=e591308ec52a9582</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Cloud Reliability Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MathWorks</t>
+          <t>Hollstadt Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Natick, MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
+          <t>https://www.indeed.com/viewjob?jk=253dcdba301dd54b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>API &amp; Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fde74cfceac685</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Senior Cloud Reliability Solutions Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>MathWorks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Natick, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=108f1ed54def2a35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>Software Engineer III - C# / Java</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=96c4f941b3b74b9a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Engineer</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Vertex AI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Software Development Engineering</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>AI/ML Solutions Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IIB and MQ Platform Engineer</t>
+          <t>Sr. Engineer - Software Development Engineering</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, MySQL, Splunk, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa947e1b4b6a598</t>
+          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>IIB and MQ Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, MySQL, Splunk, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,40 +1371,250 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa947e1b4b6a598</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>MDM Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>McLane Company</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Temple, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Vancouver, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Data Engineer â€“ Python/AI</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ARS/Rescue Rooter</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>The Hershey Company</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hershey, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Software Engineer, LLM Pipeline &amp; AI Agents</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>TSOLife</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D34" t="n">
         <v>10.4</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>AWS, S3, IAM, PostgreSQL, CI/CD, GitHub Actions, CodeBuild, Docker, Kubernetes, pytest</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0ffa9745f98e8936</t>
         </is>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
@@ -1168,35 +1168,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Engineer – Independent Contractor / Project-Based (Remote)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+          <t>https://www.indeed.com/viewjob?jk=671885b17b760d63</t>
         </is>
       </c>
     </row>
@@ -1238,52 +1238,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Java Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IIB and MQ Platform Engineer</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, MySQL, Splunk, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa947e1b4b6a598</t>
+          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>IIB and MQ Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, MySQL, Splunk, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa947e1b4b6a598</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Engineer â€“ Python/AI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>ARS/Rescue Rooter</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer, LLM Pipeline &amp; AI Agents</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TSOLife</t>
+          <t>The Hershey Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hershey, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,15 +1606,50 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Software Engineer, LLM Pipeline &amp; AI Agents</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TSOLife</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>AWS, S3, IAM, PostgreSQL, CI/CD, GitHub Actions, CodeBuild, Docker, Kubernetes, pytest</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0ffa9745f98e8936</t>
         </is>

--- a/results/job_matches_2026-08-24.xlsx
+++ b/results/job_matches_2026-08-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI-Native Builder - Europe</t>
+          <t>Senior DevOps Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>FloQast</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, SQS, ECS, IAM, RDS, Azure, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
+          <t>https://www.indeed.com/viewjob?jk=425b63d71cb4a186</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI-Native Builder- EST</t>
+          <t>AI-Native Builder - Europe</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
+          <t>https://www.indeed.com/viewjob?jk=dd55c9ebdd278646</t>
         </is>
       </c>
     </row>
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
+          <t>https://www.indeed.com/viewjob?jk=67f359adeb372509</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Native Builder- EST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vericast</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
+          <t>https://www.indeed.com/viewjob?jk=167f9d8d4ef096eb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Vericast</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Hadoop, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
+          <t>https://www.indeed.com/viewjob?jk=31f95d9c50c74e3c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
+          <t>Software Engineer – NestJS &amp; Backend Architecture</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Exadel</t>
+          <t>Quantic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Exton, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, HBase, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
+          <t>https://www.indeed.com/viewjob?jk=8a15e7186a589e33</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
+          <t>https://www.indeed.com/viewjob?jk=91d479728e749c2b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer Frontend and Backend</t>
+          <t>Middle/Senior Forward Deployed Engineer (Python, AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Exadel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d71f05982f737348</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bc4abda60b1248d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Snowflake Data Engineer Frontend and Backend</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
+          <t>https://www.indeed.com/viewjob?jk=19c0f41e24c188bc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI/ML Solutions Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BankUnited</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Miami Lakes, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Vertex AI</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b05e2a1155f8c55a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer – Independent Contractor / Project-Based (Remote)</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671885b17b760d63</t>
+          <t>https://www.indeed.com/viewjob?jk=7460cb3c8c717a9f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Engineer - Software Development Engineering</t>
+          <t>AI/ML Solutions Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>BankUnited</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Miami Lakes, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
+          <t>https://www.indeed.com/viewjob?jk=cbfd63528cbfd9b2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer</t>
+          <t>Software Engineer – Independent Contractor / Project-Based (Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
+          <t>https://www.indeed.com/viewjob?jk=671885b17b760d63</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Sr. Engineer - Software Development Engineering</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
+          <t>https://www.indeed.com/viewjob?jk=e94d5927287b9bb7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
+          <t>https://www.indeed.com/viewjob?jk=b5903b1348160f84</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Java Developer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
+          <t>https://www.indeed.com/viewjob?jk=48eda2064cab8ffc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IIB and MQ Platform Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Kafka, MySQL, Splunk, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa947e1b4b6a598</t>
+          <t>https://www.indeed.com/viewjob?jk=1abdcdcc9cd7325e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MDM Integration Engineer</t>
+          <t>Software Engineer (Basketball Operations)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>New Orleans Saints and Pelicans</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Metairie, LA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Snowflake, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
+          <t>https://www.indeed.com/viewjob?jk=19103d0713a06353</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software and DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
+          <t>AWS, Kafka, MySQL, NoSQL, Splunk, CI/CD, GitHub Actions, Maven, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c75385a79049796</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Java Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vancouver, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, SQS, SNS, RDS, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+          <t>https://www.indeed.com/viewjob?jk=1dec7a0320c1fc00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer â€“ Python/AI</t>
+          <t>IIB and MQ Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+          <t>AWS, API Gateway, RDS, Scala, Kafka, MySQL, Splunk, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa947e1b4b6a598</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>MDM Integration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ARS/Rescue Rooter</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+          <t>https://www.indeed.com/viewjob?jk=a9de9ca0c44e375f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Hershey Company</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hershey, PA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, ETL, Talend, Splunk, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+          <t>https://www.indeed.com/viewjob?jk=ee930e9556b7274f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer, LLM Pipeline &amp; AI Agents</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TSOLife</t>
+          <t>Office Ally</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Vancouver, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,227 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>IAM, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b8fe41a028c8718</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Data Engineer â€“ Python/AI</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, Oracle, MongoDB, MLOps, MLflow, CI/CD, Jenkins, Docker, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13959415bddcd4dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Azure Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ARS/Rescue Rooter</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Azure Cosmos DB, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=373e4d2080b90972</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>The Hershey Company</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Hershey, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49af7b2473aabc47</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Engineer, LLM Pipeline &amp; AI Agents</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TSOLife</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>AWS, S3, IAM, PostgreSQL, CI/CD, GitHub Actions, CodeBuild, Docker, Kubernetes, pytest</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0ffa9745f98e8936</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b90651192a24c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Alteryx Systems &amp; Platform Administrator (Onsite)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Snowflake, Oracle, SQL Server, MongoDB, Power BI, Tableau, Tableau Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74022046dd0742ee</t>
         </is>
       </c>
     </row>
